--- a/output/graficos_dimensiones/comunal_o_ocup_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:50</t>
+    <t xml:space="preserve">2026-09-09 22:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:38</t>
+    <t xml:space="preserve">2026-09-18 09:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 09:59</t>
+    <t xml:space="preserve">2026-09-23 12:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:06</t>
+    <t xml:space="preserve">2026-10-02 13:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2018_biobio.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Hualpén</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Chiguayante</t>
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Laja</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Hualqui</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:06</t>
+    <t xml:space="preserve">2026-10-04 08:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:20</t>
+    <t xml:space="preserve">2026-10-05 08:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
